--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484769_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484769_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.7691</v>
+        <v>10.9594</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6196</v>
+        <v>7.7041</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1495</v>
+        <v>3.2553</v>
       </c>
       <c r="G2" t="n">
         <v>6.7666</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4554</v>
+        <v>1.6457</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0938</v>
+        <v>1.1783</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3616</v>
+        <v>0.4674</v>
       </c>
       <c r="V2" t="n">
         <v>1.2262</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.631600000000001</v>
+        <v>10.7177</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8148</v>
+        <v>5.8479</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8169</v>
+        <v>4.8698</v>
       </c>
       <c r="G3" t="n">
         <v>7.5555</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>0.057</v>
+        <v>1.1431</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6931</v>
+        <v>0.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7502</v>
+        <v>0.8031</v>
       </c>
       <c r="V3" t="n">
         <v>0.3208</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7655</v>
+        <v>7.5651</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2534</v>
+        <v>3.7551</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5121</v>
+        <v>3.81</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5875</v>
+        <v>3.9188</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2647</v>
+        <v>0.979</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3228</v>
+        <v>2.9398</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0312</v>
+        <v>3.3625</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5746</v>
+        <v>1.2889</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4566</v>
+        <v>2.0735</v>
       </c>
       <c r="M4" t="n">
         <v>0.5564</v>
@@ -757,37 +757,37 @@
         <v>0.8663</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>2.4531</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7066</v>
+        <v>0.8724</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2039</v>
+        <v>0.3926</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5026</v>
+        <v>0.4797</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8488</v>
+        <v>0.3208</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5152</v>
+        <v>6.5346</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9168</v>
+        <v>2.6045</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5984</v>
+        <v>3.9301</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9188</v>
+        <v>3.5875</v>
       </c>
       <c r="H5" t="n">
-        <v>0.979</v>
+        <v>1.2647</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9398</v>
+        <v>2.3228</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3625</v>
+        <v>3.0312</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2889</v>
+        <v>1.5746</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0735</v>
+        <v>1.4566</v>
       </c>
       <c r="M5" t="n">
         <v>0.5564</v>
@@ -835,31 +835,31 @@
         <v>0.8663</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4531</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R5" t="n">
         <v>2.4531</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1775</v>
+        <v>1.4757</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4456</v>
+        <v>0.555</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2681</v>
+        <v>0.9206</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3208</v>
+        <v>1.8488</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.5751</v>
+        <v>4.7776</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3359</v>
+        <v>3.459</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2392</v>
+        <v>1.3186</v>
       </c>
       <c r="G6" t="n">
         <v>2.3238</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1192</v>
+        <v>1.3216</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8434</v>
+        <v>0.9665</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2757</v>
+        <v>0.3551</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>P. HURYNOWICZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.1502</v>
+        <v>2.962</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2231</v>
+        <v>0.9485</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.073</v>
+        <v>2.0135</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2833</v>
+        <v>1.6702</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3937</v>
+        <v>1.4862</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1103</v>
+        <v>0.1841</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7272</v>
+        <v>1.3521</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7771</v>
+        <v>1.7961</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9502</v>
+        <v>-0.4439</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0106</v>
+        <v>0.3181</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1708</v>
+        <v>-0.3099</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8398</v>
+        <v>0.628</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7352</v>
+        <v>0.6125</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4959</v>
+        <v>0.238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2393</v>
+        <v>0.3745</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HURYNOWICZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7974</v>
+        <v>2.6833</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8897</v>
+        <v>2.3828</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9077</v>
+        <v>0.3006</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6702</v>
+        <v>1.3896</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4862</v>
+        <v>0.4672</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1841</v>
+        <v>0.9224</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3521</v>
+        <v>2.1912</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7961</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4439</v>
+        <v>1.3984</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3181</v>
+        <v>-0.8015</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3099</v>
+        <v>-0.3256</v>
       </c>
       <c r="O8" t="n">
-        <v>0.628</v>
+        <v>-0.476</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4479</v>
+        <v>0.6519</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1793</v>
+        <v>0.1916</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2687</v>
+        <v>0.4603</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7568</v>
+        <v>2.6236</v>
       </c>
       <c r="E9" t="n">
-        <v>2.324</v>
+        <v>3.723</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4328</v>
+        <v>-1.0994</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3896</v>
+        <v>-0.2833</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4672</v>
+        <v>-0.3937</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9224</v>
+        <v>0.1103</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1912</v>
+        <v>2.7272</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7771</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3984</v>
+        <v>1.9502</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8015</v>
+        <v>-3.0106</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3256</v>
+        <v>-1.1708</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.476</v>
+        <v>-1.8398</v>
       </c>
       <c r="P9" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7254</v>
+        <v>1.2086</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1328</v>
+        <v>0.9957</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5926</v>
+        <v>0.2128</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6686</v>
+        <v>-0.84</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7511</v>
+        <v>-0.1077</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9175</v>
+        <v>-0.7323</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3464</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1335</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>0.5534</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0435</v>
+        <v>0.1417</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8682</v>
+        <v>-0.8409</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6695</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1987</v>
+        <v>-0.1458</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6856</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2957</v>
+        <v>0.7316</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3992</v>
+        <v>0.5752</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1035</v>
+        <v>0.1564</v>
       </c>
       <c r="V11" t="n">
         <v>0.3018</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6582</v>
+        <v>-4.0782</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3795</v>
+        <v>-2.9053</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2787</v>
+        <v>-1.1729</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6998</v>
@@ -1390,13 +1390,13 @@
         <v>1.6983</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2303</v>
+        <v>0.8103</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1968</v>
+        <v>0.671</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0335</v>
+        <v>0.1394</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6448</v>
+        <v>-7.355</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2872</v>
+        <v>-3.8387</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3576</v>
+        <v>-3.5163</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2519</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3427</v>
+        <v>0.6325</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1023</v>
+        <v>0.3462</v>
       </c>
       <c r="U13" t="n">
-        <v>0.445</v>
+        <v>0.2863</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4904</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.1211</v>
+        <v>35.7092</v>
       </c>
       <c r="E14" t="n">
-        <v>22.29</v>
+        <v>22.8781</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8311</v>
+        <v>12.8312</v>
       </c>
       <c r="G14" t="n">
         <v>12.945</v>
       </c>
       <c r="H14" t="n">
-        <v>4.069399999999999</v>
+        <v>4.069400000000001</v>
       </c>
       <c r="I14" t="n">
         <v>8.875399999999994</v>
@@ -1534,7 +1534,7 @@
         <v>-6.6755</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.2181</v>
+        <v>-4.218100000000001</v>
       </c>
       <c r="P14" t="n">
         <v>10.3785</v>
@@ -1546,13 +1546,13 @@
         <v>21.7005</v>
       </c>
       <c r="S14" t="n">
-        <v>11.213</v>
+        <v>11.801</v>
       </c>
       <c r="T14" t="n">
-        <v>6.415699999999999</v>
+        <v>7.003499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.797300000000001</v>
+        <v>4.7973</v>
       </c>
       <c r="V14" t="n">
         <v>0.5845999999999996</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3049</v>
+        <v>-0.6771</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5175</v>
+        <v>0.9073</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8225</v>
+        <v>-1.5844</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0253</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4684</v>
+        <v>-0.8406</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7055</v>
+        <v>-0.3157</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.763</v>
+        <v>-0.5249</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9434</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6906</v>
+        <v>-1.1733</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.4787</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7796</v>
+        <v>-1.652</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5849</v>
@@ -1780,13 +1780,13 @@
         <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8605</v>
+        <v>-1.3432</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3521</v>
+        <v>-0.9624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5084</v>
+        <v>-0.3808</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>D. ALFEREZ CANSECO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6505</v>
+        <v>-3.2614</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2045</v>
+        <v>1.5435</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.446</v>
+        <v>-4.805</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.237</v>
+        <v>0.9035</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8909</v>
+        <v>1.7562</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3461</v>
+        <v>-0.8527</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3844</v>
+        <v>4.2142</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.207</v>
+        <v>3.4653</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8226</v>
+        <v>0.7489</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8526</v>
+        <v>-3.3107</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.7091</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1687</v>
+        <v>-1.6015</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7548</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0205</v>
+        <v>-1.6179</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0669</v>
+        <v>-0.4629</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0463</v>
+        <v>-1.1551</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3208</v>
+        <v>-2.1696</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3208</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ALFEREZ CANSECO</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7051</v>
+        <v>-3.5788</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8358</v>
+        <v>-2.6987</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.541</v>
+        <v>-0.8801</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9035</v>
+        <v>-1.8442</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7562</v>
+        <v>-1.2318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8527</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2142</v>
+        <v>-0.4573</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4653</v>
+        <v>-0.5807</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7489</v>
+        <v>0.1234</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3107</v>
+        <v>-1.3869</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7091</v>
+        <v>-0.6511</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6015</v>
+        <v>-0.7358</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0616</v>
+        <v>-0.6024</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1706</v>
+        <v>-0.3544</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.8911</v>
+        <v>-0.248</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8447</v>
+        <v>-4.1714</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.991</v>
+        <v>-3.2763</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8537</v>
+        <v>-0.8952</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8442</v>
+        <v>-3.237</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2318</v>
+        <v>-2.8909</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.3461</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4573</v>
+        <v>-1.3844</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5807</v>
+        <v>-2.207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1234</v>
+        <v>0.8226</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3869</v>
+        <v>-1.8526</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6511</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7358</v>
+        <v>-1.1687</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1322</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8682</v>
+        <v>-0.5004</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.0049</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2216</v>
+        <v>-0.4955</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0845</v>
+        <v>-5.8362</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2489</v>
+        <v>-0.628</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.3334</v>
+        <v>-5.2082</v>
       </c>
       <c r="G21" t="n">
         <v>-4.6913</v>
@@ -2092,13 +2092,13 @@
         <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5443</v>
+        <v>-1.296</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1851</v>
+        <v>-0.6919</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7294</v>
+        <v>-0.6042</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8732</v>
+        <v>-7.4976</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3245</v>
+        <v>-4.545</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5487</v>
+        <v>-2.9526</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2946</v>
@@ -2170,13 +2170,13 @@
         <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9175</v>
+        <v>-1.5419</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.8812</v>
+        <v>-1.1017</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0363</v>
+        <v>-0.4402</v>
       </c>
       <c r="V22" t="n">
         <v>1.566</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.5847</v>
+        <v>-7.5935</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6193</v>
+        <v>-5.2296</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9653</v>
+        <v>-2.364</v>
       </c>
       <c r="G23" t="n">
         <v>-2.788</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.513</v>
+        <v>-1.5219</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2933</v>
+        <v>-0.9036</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2197</v>
+        <v>-0.6183</v>
       </c>
       <c r="V23" t="n">
         <v>1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-35.1212</v>
+        <v>-33.1723</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.8312</v>
+        <v>-12.8311</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.2902</v>
+        <v>-20.3415</v>
       </c>
       <c r="G24" t="n">
         <v>-12.9448</v>
@@ -2296,7 +2296,7 @@
         <v>-4.0694</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.8756</v>
+        <v>-8.875599999999999</v>
       </c>
       <c r="J24" t="n">
         <v>10.8936</v>
@@ -2326,16 +2326,16 @@
         <v>11.322</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.213</v>
+        <v>-9.2643</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.7974</v>
+        <v>-4.797499999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.415799999999999</v>
+        <v>-4.467</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5845999999999998</v>
+        <v>-0.5846</v>
       </c>
       <c r="W24" t="n">
         <v>2.7732</v>
